--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="메뉴정의서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Index" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="개정이력" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="선택조건_CH-07" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="적합성진단_CH-01" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메뉴정의서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="선택조건_CH-07" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적합성진단_CH-01" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'메뉴정의서'!$A$4:$O$64</definedName>
@@ -857,6 +857,7 @@
         </is>
       </c>
     </row>
+    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2116,7 +2117,7 @@
       </c>
       <c r="I20" s="13" t="inlineStr">
         <is>
-          <t>기본계약사항, 주계약·특약별 보장내용·가입금액, 계약관계자, 납입정보</t>
+          <t>기본계약사항, 주계약·특약별 보장내용·가입금액, 계약관계자, 납입정보, 약관·안내장 목록</t>
         </is>
       </c>
       <c r="J20" s="13" t="inlineStr">
@@ -2126,25 +2127,29 @@
       </c>
       <c r="K20" s="15" t="inlineStr">
         <is>
+          <t>약관·안내장 PDF 다운로드</t>
+        </is>
+      </c>
+      <c r="L20" s="9" t="inlineStr">
+        <is>
+          <t>보전</t>
+        </is>
+      </c>
+      <c r="M20" s="10" t="inlineStr">
+        <is>
           <t>-</t>
         </is>
       </c>
-      <c r="L20" s="9" t="inlineStr">
-        <is>
-          <t>보전</t>
-        </is>
-      </c>
-      <c r="M20" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
       <c r="N20" s="14" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="O20" s="10" t="n"/>
+      <c r="O20" s="10" t="inlineStr">
+        <is>
+          <t>v3.7: 계약별 약관(가입 당시 기준)·안내장(변액 분기 운용현황, 연간 계약안내장) PDF 다운로드</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="5" t="inlineStr">
@@ -5814,7 +5819,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E53"/>
+  <dimension ref="A1:E54"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7205,6 +7210,33 @@
       <c r="E53" s="11" t="inlineStr">
         <is>
           <t>-</t>
+        </is>
+      </c>
+    </row>
+    <row r="54">
+      <c r="A54" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B54" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C54" s="11" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="D54" s="11" t="inlineStr">
+        <is>
+          <t>계약조회: 계약별 「약관·안내장」 카드 추가 — 보험약관, 변액보험 분기 운용현황 안내장(변액 계약), 연간 계약안내장 PDF 다운로드</t>
+        </is>
+      </c>
+      <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>CT-02</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메뉴정의서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="선택조건_CH-07" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적합성진단_CH-01" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="메뉴정의서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Index" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="개정이력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="선택조건_CH-07" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="적합성진단_CH-01" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'메뉴정의서'!$A$4:$O$64</definedName>
@@ -857,7 +857,6 @@
         </is>
       </c>
     </row>
-    <row r="3"/>
     <row r="4" ht="30" customHeight="1">
       <c r="A4" s="3" t="inlineStr">
         <is>
@@ -2147,7 +2146,7 @@
       </c>
       <c r="O20" s="10" t="inlineStr">
         <is>
-          <t>v3.7: 계약별 약관(가입 당시 기준)·안내장(변액 분기 운용현황, 연간 계약안내장) PDF 다운로드</t>
+          <t>v3.7: 계약별 약관·보험상품안내장(가입 당시 기준, 각 1건) PDF 다운로드</t>
         </is>
       </c>
     </row>
@@ -5819,7 +5818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E54"/>
+  <dimension ref="A1:E55"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7235,6 +7234,33 @@
         </is>
       </c>
       <c r="E54" s="11" t="inlineStr">
+        <is>
+          <t>CT-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="55">
+      <c r="A55" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B55" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-10</t>
+        </is>
+      </c>
+      <c r="C55" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D55" s="11" t="inlineStr">
+        <is>
+          <t>계약조회 안내장을 가입 당시 「보험상품안내장」 1건으로 변경 (변액 분기 운용현황·연간 계약안내장 제외)</t>
+        </is>
+      </c>
+      <c r="E55" s="11" t="inlineStr">
         <is>
           <t>CT-02</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -5818,7 +5818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E55"/>
+  <dimension ref="A1:E56"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7263,6 +7263,33 @@
       <c r="E55" s="11" t="inlineStr">
         <is>
           <t>CT-02</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B56" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="C56" s="11" t="inlineStr">
+        <is>
+          <t>삭제</t>
+        </is>
+      </c>
+      <c r="D56" s="11" t="inlineStr">
+        <is>
+          <t>프로토타입 상단 「기획정보 보기」 스위치 제거 — 화면별 기획정보 패널, 전체메뉴 iM 대응수준 표시, 펀드변경 시연용 적합성진단일 선택 함께 제거</t>
+        </is>
+      </c>
+      <c r="E56" s="11" t="inlineStr">
+        <is>
+          <t>프로토타입 기획정보</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="메뉴정의서" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="Index" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="개정이력" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="선택조건_CH-07" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="적합성진단_CH-01" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="메뉴정의서" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Index" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="개정이력" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="선택조건_CH-07" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="적합성진단_CH-01" sheetId="5" state="visible" r:id="rId5"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'메뉴정의서'!$A$4:$O$64</definedName>
@@ -5818,7 +5818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E56"/>
+  <dimension ref="A1:E57"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7290,6 +7290,33 @@
       <c r="E56" s="11" t="inlineStr">
         <is>
           <t>프로토타입 기획정보</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B57" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C57" s="11" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="D57" s="11" t="inlineStr">
+        <is>
+          <t>공통 하단 「개인정보처리방침」에 회사 홈페이지 개인정보처리방침(https://www.imlifeins.co.kr/BE/BE_A030_2.do) 새 창 링크 연결</t>
+        </is>
+      </c>
+      <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>공통 하단</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -5818,7 +5818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E57"/>
+  <dimension ref="A1:E58"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7315,6 +7315,33 @@
         </is>
       </c>
       <c r="E57" s="11" t="inlineStr">
+        <is>
+          <t>공통 하단</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B58" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C58" s="11" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="D58" s="11" t="inlineStr">
+        <is>
+          <t>공통 하단 「신용정보활용체제」(https://www.imlifeins.co.kr/BE/BE_A032.do)·「고객권리안내」(https://www.imlifeins.co.kr/BE/BE_A031.do) 회사 홈페이지 새 창 링크 연결</t>
+        </is>
+      </c>
+      <c r="E58" s="11" t="inlineStr">
         <is>
           <t>공통 하단</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -5818,7 +5818,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E58"/>
+  <dimension ref="A1:E59"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7342,6 +7342,33 @@
         </is>
       </c>
       <c r="E58" s="11" t="inlineStr">
+        <is>
+          <t>공통 하단</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B59" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C59" s="11" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="D59" s="11" t="inlineStr">
+        <is>
+          <t>공통 하단 「보험사기신고」(https://www.imlifeins.co.kr/BB/BB_C020.do)·「전자민원」(https://www.imlifeins.co.kr/BB/BB_B010.do) 회사 홈페이지 새 창 링크 연결, 링크 항목 굵게 강조</t>
+        </is>
+      </c>
+      <c r="E59" s="11" t="inlineStr">
         <is>
           <t>공통 하단</t>
         </is>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -823,7 +823,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:O64"/>
+  <dimension ref="A1:O65"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.7109375" defaultRowHeight="15"/>
   <cols>
     <col width="9" customWidth="1" min="1" max="1"/>
@@ -853,7 +853,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>60개 화면(업무 52 + 공통 8) · v3.7 · 메뉴명=공개 사이트맵 확인 / 공통(CM)=프로토타입 v3.7 반영 / 회색 글씨 항목=추정(로그인 화면 미확인) / 메뉴ID: 업무코드-번호 (CM 공통 · MY · CT · PY · PM · CH · LN · CF · CS 서류·안내)</t>
+          <t>61개 화면(업무 53 + 공통 8) · v3.7 · 메뉴명=공개 사이트맵 확인 / 공통(CM)=프로토타입 v3.7 반영 / 회색 글씨 항목=추정(로그인 화면 미확인) / 메뉴ID: 업무코드-번호 (CM 공통 · MY · CT · PY · PM · CH · LN · CF · CS 서류·안내)</t>
         </is>
       </c>
     </row>
@@ -3625,7 +3625,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>CH-01</t>
+          <t>CH-10</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -3638,9 +3638,9 @@
           <t>보험계약관리</t>
         </is>
       </c>
-      <c r="D41" s="8" t="inlineStr">
-        <is>
-          <t>변액보험 펀드변경/관리</t>
+      <c r="D41" s="19" t="inlineStr">
+        <is>
+          <t>계약관계자변경</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
@@ -3650,42 +3650,42 @@
       </c>
       <c r="F41" s="10" t="inlineStr">
         <is>
-          <t>T4 단일폼 변경</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>변액 계약자</t>
+          <t>계약자(피보험자 동의 필요)</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
-        </is>
-      </c>
-      <c r="I41" s="32" t="inlineStr">
-        <is>
-          <t>펀드별 위험등급·현재 비율·1년 수익률, 적립금·잔여 변경 횟수·투자성향, 최근 적합성진단일·투자 가능 범위, 변경 후 포트폴리오 위험등급(실시간), 변경 전후 비교(편입비율 막대·펀드별 증감·포트폴리오 위험등급·자동재배분·남은 변경 횟수)</t>
-        </is>
-      </c>
-      <c r="J41" s="32" t="inlineStr">
-        <is>
-          <t>변경 펀드·비율(합계 100%), 자동재배분 / (필요 시) 적합성진단 5문항</t>
-        </is>
-      </c>
-      <c r="K41" s="32" t="inlineStr">
-        <is>
-          <t>변경 전후 비교 확인 후 인증 → 변경 접수·적용일 안내 / 진단 결과 불가 시 변경 불가·익일 재진행 안내</t>
-        </is>
-      </c>
-      <c r="L41" s="12" t="inlineStr">
-        <is>
-          <t>변액</t>
-        </is>
-      </c>
-      <c r="M41" s="33" t="inlineStr">
-        <is>
-          <t>적합성원칙(금융소비자보호법) · 투자위험 고지 · 진단 후 3년 유효 · 부적합 시 당일 재진단 불가</t>
+          <t>A1 인증서+추가인증</t>
+        </is>
+      </c>
+      <c r="I41" s="13" t="inlineStr">
+        <is>
+          <t>현재 수익자(만기·사망·기타)</t>
+        </is>
+      </c>
+      <c r="J41" s="13" t="inlineStr">
+        <is>
+          <t>변경 수익자 정보, 피보험자 동의</t>
+        </is>
+      </c>
+      <c r="K41" s="13" t="inlineStr">
+        <is>
+          <t>변경 완료 안내</t>
+        </is>
+      </c>
+      <c r="L41" s="9" t="inlineStr">
+        <is>
+          <t>보전</t>
+        </is>
+      </c>
+      <c r="M41" s="11" t="inlineStr">
+        <is>
+          <t>사망수익자 변경 시 피보험자 동의(상법)</t>
         </is>
       </c>
       <c r="N41" s="14" t="inlineStr">
@@ -3693,16 +3693,12 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O41" s="34" t="inlineStr">
-        <is>
-          <t>v3.4: 변경 후 비율 입력 → 다음 → 적합성진단 필요 판단(①진단 후 3년 경과 ②변경 후 편입비율 위험 &gt; 현재 투자성향) → (필요 시) 진단 → 변경 전후 비교 → 인증 → 완료 / 진단 불가 시 익일 재진행 안내 · 변경 내용 없으면 진행 불가 (상세: 「적합성진단_CH-01」 시트) / 변액 계약이 2건 이상이면 상단 계약 탭으로 선택(변액보험 조회·펀드변경 간 선택 유지, 계약카드 「펀드 수익률」에서 진입 시 해당 계약 선택)</t>
-        </is>
-      </c>
+      <c r="O41" s="10" t="n"/>
     </row>
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>CH-02</t>
+          <t>CH-05</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -3717,7 +3713,7 @@
       </c>
       <c r="D42" s="8" t="inlineStr">
         <is>
-          <t>감액완납</t>
+          <t>보험기간/연금개시연도 변경</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -3742,12 +3738,12 @@
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>감액완납 후 가입금액·보장, 이후 납입 면제</t>
+          <t>연금 계약 카드(현재 연금개시 나이·일자, 납입 현황, 적립금), 변경 가능 범위(55~80세)</t>
         </is>
       </c>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>확인 동의</t>
+          <t>대상 계약(카드 라디오 선택), 변경 후 연금개시 나이</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -3760,9 +3756,9 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M42" s="11" t="inlineStr">
-        <is>
-          <t>특약 소멸 고지</t>
+      <c r="M42" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N42" s="16" t="inlineStr">
@@ -3770,12 +3766,16 @@
           <t>없음</t>
         </is>
       </c>
-      <c r="O42" s="10" t="n"/>
+      <c r="O42" s="10" t="inlineStr">
+        <is>
+          <t>선택 → 입력 → 인증 → 완료 (확인 단계 생략)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>CH-03</t>
+          <t>CH-07</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>특약해지</t>
+          <t>연금개시유형 선택/변경</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>연금 계약자</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -3813,14 +3813,14 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I43" s="13" t="inlineStr">
-        <is>
-          <t>특약 목록, 해지 시 환급금·변경 후 보험료</t>
-        </is>
-      </c>
-      <c r="J43" s="13" t="inlineStr">
-        <is>
-          <t>해지 특약 선택</t>
+      <c r="I43" s="32" t="inlineStr">
+        <is>
+          <t>연금 계약(선택 단계), 선택 요약·월 환산 예상액·회당 예상 연금액(지급주기 반영, 예시)</t>
+        </is>
+      </c>
+      <c r="J43" s="32" t="inlineStr">
+        <is>
+          <t>연금유형, 개인형/부부형, 연금비율, 체증형태, 체증기간, 체증율, 확정기간, 보증기간, 지급주기, 조기집중형보장배수 (10개 선택조건)</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -3833,22 +3833,26 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M43" s="11" t="inlineStr">
-        <is>
-          <t>변경 전후 보장 비교 고지</t>
-        </is>
-      </c>
-      <c r="N43" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O43" s="10" t="n"/>
+      <c r="M43" s="33" t="inlineStr">
+        <is>
+          <t>개시 후 변경 제한 고지 / 예상 연금액은 예시(확정 아님)</t>
+        </is>
+      </c>
+      <c r="N43" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O43" s="34" t="inlineStr">
+        <is>
+          <t>v3.3: 연금유형별 고정값 규칙 적용(상세: 「선택조건_CH-07」 시트) · 고정 항목은 고정값만 표시·선택 불가 · 입력 영역 PC 2열/모바일 2열(긴 항목 1열) 촘촘한 버튼형 배치</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>CH-04</t>
+          <t>CH-11</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -3863,12 +3867,12 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>보험계약 해지</t>
+          <t>연금전환 사전신청</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>지급</t>
+          <t>신청</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
@@ -3878,50 +3882,54 @@
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>계약자(=수익자)</t>
+          <t>계약자(종신보험)</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I44" s="13" t="inlineStr">
         <is>
-          <t>예상 해지환급금, 대출 상계액, 실수령액, 해지 시 불이익, 유지 권유</t>
+          <t>전환 가능 종신보험(적립금), 전환 시점 예상 적립금·연금액(예시)</t>
         </is>
       </c>
       <c r="J44" s="13" t="inlineStr">
         <is>
-          <t>해지 사유, 계좌, 확인 동의</t>
+          <t>대상 계약, 연금 전환 나이, 연금 유형, 지급 주기, 연금 받을 계좌</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>해지 완료·환급금 입금</t>
-        </is>
-      </c>
-      <c r="L44" s="12" t="inlineStr">
-        <is>
-          <t>지급</t>
-        </is>
-      </c>
-      <c r="M44" s="11" t="inlineStr">
-        <is>
-          <t>해지 불이익 설명·확인(금소법)</t>
-        </is>
-      </c>
-      <c r="N44" s="17" t="inlineStr">
-        <is>
-          <t>부분</t>
-        </is>
-      </c>
-      <c r="O44" s="10" t="n"/>
+          <t>사전신청 접수·전환 예정일 30일 전 알림톡 안내</t>
+        </is>
+      </c>
+      <c r="L44" s="9" t="inlineStr">
+        <is>
+          <t>보전</t>
+        </is>
+      </c>
+      <c r="M44" s="10" t="inlineStr">
+        <is>
+          <t>사망보장 소멸·감소 안내</t>
+        </is>
+      </c>
+      <c r="N44" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O44" s="10" t="inlineStr">
+        <is>
+          <t>v3.7 신규: 전환 예정일 전까지 변경·취소 가능</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="5" t="inlineStr">
         <is>
-          <t>CH-05</t>
+          <t>CH-01</t>
         </is>
       </c>
       <c r="B45" s="7" t="inlineStr">
@@ -3936,7 +3944,7 @@
       </c>
       <c r="D45" s="8" t="inlineStr">
         <is>
-          <t>보험기간/연금개시연도 변경</t>
+          <t>변액보험 펀드변경/관리</t>
         </is>
       </c>
       <c r="E45" s="9" t="inlineStr">
@@ -3946,12 +3954,12 @@
       </c>
       <c r="F45" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T4 단일폼 변경</t>
         </is>
       </c>
       <c r="G45" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>변액 계약자</t>
         </is>
       </c>
       <c r="H45" s="12" t="inlineStr">
@@ -3959,46 +3967,46 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I45" s="13" t="inlineStr">
-        <is>
-          <t>연금 계약 카드(현재 연금개시 나이·일자, 납입 현황, 적립금), 변경 가능 범위(55~80세)</t>
-        </is>
-      </c>
-      <c r="J45" s="13" t="inlineStr">
-        <is>
-          <t>대상 계약(카드 라디오 선택), 변경 후 연금개시 나이</t>
-        </is>
-      </c>
-      <c r="K45" s="13" t="inlineStr">
-        <is>
-          <t>변경 완료 안내</t>
-        </is>
-      </c>
-      <c r="L45" s="9" t="inlineStr">
-        <is>
-          <t>보전</t>
-        </is>
-      </c>
-      <c r="M45" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N45" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O45" s="10" t="inlineStr">
-        <is>
-          <t>선택 → 입력 → 인증 → 완료 (확인 단계 생략)</t>
+      <c r="I45" s="32" t="inlineStr">
+        <is>
+          <t>펀드별 위험등급·현재 비율·1년 수익률, 적립금·잔여 변경 횟수·투자성향, 최근 적합성진단일·투자 가능 범위, 변경 후 포트폴리오 위험등급(실시간), 변경 전후 비교(편입비율 막대·펀드별 증감·포트폴리오 위험등급·자동재배분·남은 변경 횟수)</t>
+        </is>
+      </c>
+      <c r="J45" s="32" t="inlineStr">
+        <is>
+          <t>변경 펀드·비율(합계 100%), 자동재배분 / (필요 시) 적합성진단 5문항</t>
+        </is>
+      </c>
+      <c r="K45" s="32" t="inlineStr">
+        <is>
+          <t>변경 전후 비교 확인 후 인증 → 변경 접수·적용일 안내 / 진단 결과 불가 시 변경 불가·익일 재진행 안내</t>
+        </is>
+      </c>
+      <c r="L45" s="12" t="inlineStr">
+        <is>
+          <t>변액</t>
+        </is>
+      </c>
+      <c r="M45" s="33" t="inlineStr">
+        <is>
+          <t>적합성원칙(금융소비자보호법) · 투자위험 고지 · 진단 후 3년 유효 · 부적합 시 당일 재진단 불가</t>
+        </is>
+      </c>
+      <c r="N45" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O45" s="34" t="inlineStr">
+        <is>
+          <t>v3.4: 변경 후 비율 입력 → 다음 → 적합성진단 필요 판단(①진단 후 3년 경과 ②변경 후 편입비율 위험 &gt; 현재 투자성향) → (필요 시) 진단 → 변경 전후 비교 → 인증 → 완료 / 진단 불가 시 익일 재진행 안내 · 변경 내용 없으면 진행 불가 (상세: 「적합성진단_CH-01」 시트) / 변액 계약이 2건 이상이면 상단 계약 탭으로 선택(변액보험 조회·펀드변경 간 선택 유지, 계약카드 「펀드 수익률」에서 진입 시 해당 계약 선택)</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="5" t="inlineStr">
         <is>
-          <t>CH-06</t>
+          <t>CH-02</t>
         </is>
       </c>
       <c r="B46" s="7" t="inlineStr">
@@ -4013,12 +4021,12 @@
       </c>
       <c r="D46" s="8" t="inlineStr">
         <is>
-          <t>청약 철회</t>
+          <t>감액완납</t>
         </is>
       </c>
       <c r="E46" s="9" t="inlineStr">
         <is>
-          <t>지급</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="F46" s="10" t="inlineStr">
@@ -4038,17 +4046,17 @@
       </c>
       <c r="I46" s="13" t="inlineStr">
         <is>
-          <t>철회 가능 계약·기한, 반환 보험료</t>
+          <t>감액완납 후 가입금액·보장, 이후 납입 면제</t>
         </is>
       </c>
       <c r="J46" s="13" t="inlineStr">
         <is>
-          <t>철회 사유, 환불계좌</t>
+          <t>확인 동의</t>
         </is>
       </c>
       <c r="K46" s="13" t="inlineStr">
         <is>
-          <t>철회 접수·환불 예정일</t>
+          <t>변경 완료 안내</t>
         </is>
       </c>
       <c r="L46" s="9" t="inlineStr">
@@ -4058,12 +4066,12 @@
       </c>
       <c r="M46" s="11" t="inlineStr">
         <is>
-          <t>청약철회권(금소법)</t>
+          <t>특약 소멸 고지</t>
         </is>
       </c>
       <c r="N46" s="16" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="O46" s="10" t="n"/>
@@ -4071,7 +4079,7 @@
     <row r="47">
       <c r="A47" s="5" t="inlineStr">
         <is>
-          <t>CH-07</t>
+          <t>CH-03</t>
         </is>
       </c>
       <c r="B47" s="7" t="inlineStr">
@@ -4086,7 +4094,7 @@
       </c>
       <c r="D47" s="8" t="inlineStr">
         <is>
-          <t>연금개시유형 선택/변경</t>
+          <t>특약해지</t>
         </is>
       </c>
       <c r="E47" s="9" t="inlineStr">
@@ -4101,7 +4109,7 @@
       </c>
       <c r="G47" s="11" t="inlineStr">
         <is>
-          <t>연금 계약자</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H47" s="12" t="inlineStr">
@@ -4109,14 +4117,14 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I47" s="32" t="inlineStr">
-        <is>
-          <t>연금 계약(선택 단계), 선택 요약·월 환산 예상액·회당 예상 연금액(지급주기 반영, 예시)</t>
-        </is>
-      </c>
-      <c r="J47" s="32" t="inlineStr">
-        <is>
-          <t>연금유형, 개인형/부부형, 연금비율, 체증형태, 체증기간, 체증율, 확정기간, 보증기간, 지급주기, 조기집중형보장배수 (10개 선택조건)</t>
+      <c r="I47" s="13" t="inlineStr">
+        <is>
+          <t>특약 목록, 해지 시 환급금·변경 후 보험료</t>
+        </is>
+      </c>
+      <c r="J47" s="13" t="inlineStr">
+        <is>
+          <t>해지 특약 선택</t>
         </is>
       </c>
       <c r="K47" s="13" t="inlineStr">
@@ -4129,26 +4137,22 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M47" s="33" t="inlineStr">
-        <is>
-          <t>개시 후 변경 제한 고지 / 예상 연금액은 예시(확정 아님)</t>
-        </is>
-      </c>
-      <c r="N47" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O47" s="34" t="inlineStr">
-        <is>
-          <t>v3.3: 연금유형별 고정값 규칙 적용(상세: 「선택조건_CH-07」 시트) · 고정 항목은 고정값만 표시·선택 불가 · 입력 영역 PC 2열/모바일 2열(긴 항목 1열) 촘촘한 버튼형 배치</t>
-        </is>
-      </c>
+      <c r="M47" s="11" t="inlineStr">
+        <is>
+          <t>변경 전후 보장 비교 고지</t>
+        </is>
+      </c>
+      <c r="N47" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O47" s="10" t="n"/>
     </row>
     <row r="48">
       <c r="A48" s="5" t="inlineStr">
         <is>
-          <t>CH-08</t>
+          <t>CH-04</t>
         </is>
       </c>
       <c r="B48" s="7" t="inlineStr">
@@ -4163,22 +4167,22 @@
       </c>
       <c r="D48" s="8" t="inlineStr">
         <is>
-          <t>금융정보보호 신청/해제</t>
+          <t>보험계약 해지</t>
         </is>
       </c>
       <c r="E48" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="F48" s="10" t="inlineStr">
         <is>
-          <t>T4 단일폼 변경</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G48" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>계약자(=수익자)</t>
         </is>
       </c>
       <c r="H48" s="12" t="inlineStr">
@@ -4188,35 +4192,35 @@
       </c>
       <c r="I48" s="13" t="inlineStr">
         <is>
-          <t>현재 보호 설정 여부</t>
+          <t>예상 해지환급금, 대출 상계액, 실수령액, 해지 시 불이익, 유지 권유</t>
         </is>
       </c>
       <c r="J48" s="13" t="inlineStr">
         <is>
-          <t>신청·해제</t>
+          <t>해지 사유, 계좌, 확인 동의</t>
         </is>
       </c>
       <c r="K48" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 알림</t>
-        </is>
-      </c>
-      <c r="L48" s="9" t="inlineStr">
-        <is>
-          <t>고객</t>
-        </is>
-      </c>
-      <c r="M48" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N48" s="16" t="inlineStr">
-        <is>
-          <t>미확인</t>
-        </is>
-      </c>
-      <c r="O48" s="11" t="n"/>
+          <t>해지 완료·환급금 입금</t>
+        </is>
+      </c>
+      <c r="L48" s="12" t="inlineStr">
+        <is>
+          <t>지급</t>
+        </is>
+      </c>
+      <c r="M48" s="11" t="inlineStr">
+        <is>
+          <t>해지 불이익 설명·확인(금소법)</t>
+        </is>
+      </c>
+      <c r="N48" s="17" t="inlineStr">
+        <is>
+          <t>부분</t>
+        </is>
+      </c>
+      <c r="O48" s="10" t="n"/>
     </row>
     <row r="49">
       <c r="A49" s="5" t="inlineStr">
@@ -4236,7 +4240,7 @@
       </c>
       <c r="D49" s="18" t="inlineStr">
         <is>
-          <t>대리청구인지정 등록</t>
+          <t>대리청구인 지정/등록</t>
         </is>
       </c>
       <c r="E49" s="9" t="inlineStr">
@@ -4294,7 +4298,7 @@
     <row r="50">
       <c r="A50" s="5" t="inlineStr">
         <is>
-          <t>CH-10</t>
+          <t>CH-08</t>
         </is>
       </c>
       <c r="B50" s="7" t="inlineStr">
@@ -4307,9 +4311,9 @@
           <t>보험계약관리</t>
         </is>
       </c>
-      <c r="D50" s="19" t="inlineStr">
-        <is>
-          <t>계약관계자변경</t>
+      <c r="D50" s="8" t="inlineStr">
+        <is>
+          <t>금융정보보호 신청/해제</t>
         </is>
       </c>
       <c r="E50" s="9" t="inlineStr">
@@ -4319,12 +4323,12 @@
       </c>
       <c r="F50" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T4 단일폼 변경</t>
         </is>
       </c>
       <c r="G50" s="11" t="inlineStr">
         <is>
-          <t>계약자(피보험자 동의 필요)</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H50" s="12" t="inlineStr">
@@ -4334,70 +4338,70 @@
       </c>
       <c r="I50" s="13" t="inlineStr">
         <is>
-          <t>현재 수익자(만기·사망·기타)</t>
+          <t>현재 보호 설정 여부</t>
         </is>
       </c>
       <c r="J50" s="13" t="inlineStr">
         <is>
-          <t>변경 수익자 정보, 피보험자 동의</t>
+          <t>신청·해제</t>
         </is>
       </c>
       <c r="K50" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 안내</t>
+          <t>변경 완료 알림</t>
         </is>
       </c>
       <c r="L50" s="9" t="inlineStr">
         <is>
-          <t>보전</t>
-        </is>
-      </c>
-      <c r="M50" s="11" t="inlineStr">
-        <is>
-          <t>사망수익자 변경 시 피보험자 동의(상법)</t>
-        </is>
-      </c>
-      <c r="N50" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O50" s="10" t="n"/>
+          <t>고객</t>
+        </is>
+      </c>
+      <c r="M50" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N50" s="16" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="O50" s="11" t="n"/>
     </row>
     <row r="51">
       <c r="A51" s="5" t="inlineStr">
         <is>
-          <t>LN-01</t>
+          <t>CH-06</t>
         </is>
       </c>
       <c r="B51" s="7" t="inlineStr">
         <is>
-          <t>대출</t>
+          <t>보험</t>
         </is>
       </c>
       <c r="C51" s="7" t="inlineStr">
         <is>
-          <t>대출조회</t>
+          <t>보험계약관리</t>
         </is>
       </c>
       <c r="D51" s="8" t="inlineStr">
         <is>
-          <t>대출내역 조회</t>
+          <t>청약철회</t>
         </is>
       </c>
       <c r="E51" s="9" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="F51" s="10" t="inlineStr">
         <is>
-          <t>T2 목록+상세</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G51" s="11" t="inlineStr">
         <is>
-          <t>차주</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H51" s="12" t="inlineStr">
@@ -4407,30 +4411,30 @@
       </c>
       <c r="I51" s="13" t="inlineStr">
         <is>
-          <t>대출종류, 대출일, 잔액, 적용이율, 이자 납입일, 미납이자</t>
-        </is>
-      </c>
-      <c r="J51" s="15" t="inlineStr">
-        <is>
-          <t>-</t>
+          <t>철회 가능 계약·기한, 반환 보험료</t>
+        </is>
+      </c>
+      <c r="J51" s="13" t="inlineStr">
+        <is>
+          <t>철회 사유, 환불계좌</t>
         </is>
       </c>
       <c r="K51" s="13" t="inlineStr">
         <is>
-          <t>상환·증명서 연결</t>
+          <t>철회 접수·환불 예정일</t>
         </is>
       </c>
       <c r="L51" s="9" t="inlineStr">
         <is>
-          <t>대출</t>
-        </is>
-      </c>
-      <c r="M51" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N51" s="14" t="inlineStr">
+          <t>보전</t>
+        </is>
+      </c>
+      <c r="M51" s="11" t="inlineStr">
+        <is>
+          <t>청약철회권(금소법)</t>
+        </is>
+      </c>
+      <c r="N51" s="16" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
@@ -4440,7 +4444,7 @@
     <row r="52">
       <c r="A52" s="5" t="inlineStr">
         <is>
-          <t>LN-02</t>
+          <t>LN-01</t>
         </is>
       </c>
       <c r="B52" s="7" t="inlineStr">
@@ -4450,47 +4454,47 @@
       </c>
       <c r="C52" s="7" t="inlineStr">
         <is>
-          <t>보험계약대출</t>
+          <t>대출조회</t>
         </is>
       </c>
       <c r="D52" s="8" t="inlineStr">
         <is>
-          <t>보험계약대출 신청</t>
+          <t>대출내역 조회</t>
         </is>
       </c>
       <c r="E52" s="9" t="inlineStr">
         <is>
-          <t>지급</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="F52" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T2 목록+상세</t>
         </is>
       </c>
       <c r="G52" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>차주</t>
         </is>
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I52" s="13" t="inlineStr">
         <is>
-          <t>[선택] 전체 대출 가능금액, 대출 가능 계약 수, 대출 가능 계약 목록(이율 낮은 순 · 계약별 대출 가능금액·대출이율·기존 대출잔액), 계약별 배정 대출금액·예상 월 이자, 배정 합계 / [확인·완료] 대출 실행 계약 카드(계약별 대출금액·적용 이율·예상 월 이자), 평균 적용 이율, 예상 월 이자 합계</t>
-        </is>
-      </c>
-      <c r="J52" s="13" t="inlineStr">
-        <is>
-          <t>[선택] 대출 신청금액(10만원 이상 ~ 전체 대출 가능금액) / [입력] 입금계좌, 필수 동의 (대출 신청금액 입력 없음)</t>
+          <t>대출종류, 대출일, 잔액, 적용이율, 이자 납입일, 미납이자</t>
+        </is>
+      </c>
+      <c r="J52" s="15" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="K52" s="13" t="inlineStr">
         <is>
-          <t>대출 실행·입금 안내, 대출 실행 계약을 카드로 표시(이율·대출금액)</t>
+          <t>상환·증명서 연결</t>
         </is>
       </c>
       <c r="L52" s="9" t="inlineStr">
@@ -4498,9 +4502,9 @@
           <t>대출</t>
         </is>
       </c>
-      <c r="M52" s="11" t="inlineStr">
-        <is>
-          <t>대출 상품설명·약정 전자서명</t>
+      <c r="M52" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N52" s="14" t="inlineStr">
@@ -4508,16 +4512,12 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O52" s="10" t="inlineStr">
-        <is>
-          <t>v3.1: 신청금액이 대출 가능금액보다 적으면 대출이율이 낮은 계약부터 순서대로 배정(계약별 가능금액까지 채운 뒤 다음 계약)</t>
-        </is>
-      </c>
+      <c r="O52" s="10" t="n"/>
     </row>
     <row r="53">
       <c r="A53" s="5" t="inlineStr">
         <is>
-          <t>LN-03</t>
+          <t>LN-02</t>
         </is>
       </c>
       <c r="B53" s="7" t="inlineStr">
@@ -4532,17 +4532,17 @@
       </c>
       <c r="D53" s="8" t="inlineStr">
         <is>
-          <t>보험계약대출 신청 현황 조회/취소</t>
+          <t>보험계약대출 신청</t>
         </is>
       </c>
       <c r="E53" s="9" t="inlineStr">
         <is>
-          <t>조회</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="F53" s="10" t="inlineStr">
         <is>
-          <t>T2 목록+상세</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G53" s="11" t="inlineStr">
@@ -4552,22 +4552,22 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I53" s="13" t="inlineStr">
         <is>
-          <t>신청일, 신청금액, 처리상태</t>
+          <t>[선택] 전체 대출 가능금액, 대출 가능 계약 수, 대출 가능 계약 목록(이율 낮은 순 · 계약별 대출 가능금액·대출이율·기존 대출잔액), 계약별 배정 대출금액·예상 월 이자, 배정 합계 / [확인·완료] 대출 실행 계약 카드(계약별 대출금액·적용 이율·예상 월 이자), 평균 적용 이율, 예상 월 이자 합계</t>
         </is>
       </c>
       <c r="J53" s="13" t="inlineStr">
         <is>
-          <t>취소 대상</t>
+          <t>[선택] 대출 신청금액(10만원 이상 ~ 전체 대출 가능금액) / [입력] 입금계좌, 필수 동의 (대출 신청금액 입력 없음)</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>취소 완료 안내</t>
+          <t>대출 실행·입금 안내, 대출 실행 계약을 카드로 표시(이율·대출금액)</t>
         </is>
       </c>
       <c r="L53" s="9" t="inlineStr">
@@ -4577,20 +4577,24 @@
       </c>
       <c r="M53" s="11" t="inlineStr">
         <is>
-          <t>대출계약 철회권(금소법)</t>
-        </is>
-      </c>
-      <c r="N53" s="16" t="inlineStr">
-        <is>
-          <t>미확인</t>
-        </is>
-      </c>
-      <c r="O53" s="10" t="n"/>
+          <t>대출 상품설명·약정 전자서명</t>
+        </is>
+      </c>
+      <c r="N53" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O53" s="10" t="inlineStr">
+        <is>
+          <t>v3.1: 신청금액이 대출 가능금액보다 적으면 대출이율이 낮은 계약부터 순서대로 배정(계약별 가능금액까지 채운 뒤 다음 계약)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="5" t="inlineStr">
         <is>
-          <t>LN-04</t>
+          <t>LN-03</t>
         </is>
       </c>
       <c r="B54" s="7" t="inlineStr">
@@ -4605,22 +4609,22 @@
       </c>
       <c r="D54" s="8" t="inlineStr">
         <is>
-          <t>보험계약대출 상환/이자납입</t>
+          <t>보험계약대출 신청 현황 조회/취소</t>
         </is>
       </c>
       <c r="E54" s="9" t="inlineStr">
         <is>
-          <t>입금</t>
+          <t>조회</t>
         </is>
       </c>
       <c r="F54" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T2 목록+상세</t>
         </is>
       </c>
       <c r="G54" s="11" t="inlineStr">
         <is>
-          <t>차주</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H54" s="12" t="inlineStr">
@@ -4630,17 +4634,17 @@
       </c>
       <c r="I54" s="13" t="inlineStr">
         <is>
-          <t>대출 잔액, 미납 이자, 상환 후 잔액</t>
+          <t>신청일, 신청금액, 처리상태</t>
         </is>
       </c>
       <c r="J54" s="13" t="inlineStr">
         <is>
-          <t>상환구분(전액·일부·이자), 금액, 출금계좌</t>
+          <t>취소 대상</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>상환 완료 안내</t>
+          <t>취소 완료 안내</t>
         </is>
       </c>
       <c r="L54" s="9" t="inlineStr">
@@ -4648,14 +4652,14 @@
           <t>대출</t>
         </is>
       </c>
-      <c r="M54" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N54" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
+      <c r="M54" s="11" t="inlineStr">
+        <is>
+          <t>대출계약 철회권(금소법)</t>
+        </is>
+      </c>
+      <c r="N54" s="16" t="inlineStr">
+        <is>
+          <t>미확인</t>
         </is>
       </c>
       <c r="O54" s="10" t="n"/>
@@ -4663,7 +4667,7 @@
     <row r="55">
       <c r="A55" s="5" t="inlineStr">
         <is>
-          <t>LN-05</t>
+          <t>LN-04</t>
         </is>
       </c>
       <c r="B55" s="7" t="inlineStr">
@@ -4678,17 +4682,17 @@
       </c>
       <c r="D55" s="8" t="inlineStr">
         <is>
-          <t>보험계약대출 정액분할상환</t>
+          <t>보험계약대출 상환/이자납입</t>
         </is>
       </c>
       <c r="E55" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>입금</t>
         </is>
       </c>
       <c r="F55" s="10" t="inlineStr">
         <is>
-          <t>T4 단일폼 변경</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G55" s="11" t="inlineStr">
@@ -4703,17 +4707,17 @@
       </c>
       <c r="I55" s="13" t="inlineStr">
         <is>
-          <t>분할상환 가능 대출, 월 상환액 예시</t>
+          <t>대출 잔액, 미납 이자, 상환 후 잔액</t>
         </is>
       </c>
       <c r="J55" s="13" t="inlineStr">
         <is>
-          <t>월 상환액·이체일·계좌</t>
+          <t>상환구분(전액·일부·이자), 금액, 출금계좌</t>
         </is>
       </c>
       <c r="K55" s="13" t="inlineStr">
         <is>
-          <t>신청 완료 안내</t>
+          <t>상환 완료 안내</t>
         </is>
       </c>
       <c r="L55" s="9" t="inlineStr">
@@ -4736,7 +4740,7 @@
     <row r="56">
       <c r="A56" s="5" t="inlineStr">
         <is>
-          <t>LN-06</t>
+          <t>LN-05</t>
         </is>
       </c>
       <c r="B56" s="7" t="inlineStr">
@@ -4746,12 +4750,12 @@
       </c>
       <c r="C56" s="7" t="inlineStr">
         <is>
-          <t>보험계약대출 관리</t>
-        </is>
-      </c>
-      <c r="D56" s="18" t="inlineStr">
-        <is>
-          <t>원리금 자동이체 신청/해지</t>
+          <t>보험계약대출</t>
+        </is>
+      </c>
+      <c r="D56" s="8" t="inlineStr">
+        <is>
+          <t>보험계약대출 정액분할상환</t>
         </is>
       </c>
       <c r="E56" s="9" t="inlineStr">
@@ -4771,22 +4775,22 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I56" s="13" t="inlineStr">
         <is>
-          <t>현재 이자 이체 계좌·이체일</t>
+          <t>분할상환 가능 대출, 월 상환액 예시</t>
         </is>
       </c>
       <c r="J56" s="13" t="inlineStr">
         <is>
-          <t>계좌, 이체일, 신청·해지</t>
+          <t>월 상환액·이체일·계좌</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 알림</t>
+          <t>신청 완료 안내</t>
         </is>
       </c>
       <c r="L56" s="9" t="inlineStr">
@@ -4804,67 +4808,67 @@
           <t>있음</t>
         </is>
       </c>
-      <c r="O56" s="11" t="n"/>
+      <c r="O56" s="10" t="n"/>
     </row>
     <row r="57">
       <c r="A57" s="5" t="inlineStr">
         <is>
-          <t>CF-01</t>
+          <t>LN-06</t>
         </is>
       </c>
       <c r="B57" s="7" t="inlineStr">
         <is>
-          <t>증명서발급</t>
+          <t>대출</t>
         </is>
       </c>
       <c r="C57" s="7" t="inlineStr">
         <is>
-          <t>보험</t>
+          <t>보험계약대출 관리</t>
         </is>
       </c>
       <c r="D57" s="18" t="inlineStr">
         <is>
-          <t>소득/세액공제 납입증명서</t>
+          <t>원리금 자동이체 신청/해지</t>
         </is>
       </c>
       <c r="E57" s="9" t="inlineStr">
         <is>
-          <t>발급</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="F57" s="10" t="inlineStr">
         <is>
-          <t>T5 발급</t>
+          <t>T4 단일폼 변경</t>
         </is>
       </c>
       <c r="G57" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>차주</t>
         </is>
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I57" s="13" t="inlineStr">
         <is>
-          <t>대상 연도, 계약별 공제대상 납입액</t>
+          <t>현재 이자 이체 계좌·이체일</t>
         </is>
       </c>
       <c r="J57" s="13" t="inlineStr">
         <is>
-          <t>연도, 수신방법(출력·PDF·이메일·팩스)</t>
+          <t>계좌, 이체일, 신청·해지</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>즉시 발급</t>
+          <t>변경 완료 알림</t>
         </is>
       </c>
       <c r="L57" s="9" t="inlineStr">
         <is>
-          <t>수금</t>
+          <t>대출</t>
         </is>
       </c>
       <c r="M57" s="10" t="inlineStr">
@@ -4872,17 +4876,17 @@
           <t>-</t>
         </is>
       </c>
-      <c r="N57" s="16" t="inlineStr">
+      <c r="N57" s="14" t="inlineStr">
         <is>
           <t>있음</t>
         </is>
       </c>
-      <c r="O57" s="10" t="n"/>
+      <c r="O57" s="11" t="n"/>
     </row>
     <row r="58">
       <c r="A58" s="5" t="inlineStr">
         <is>
-          <t>CF-02</t>
+          <t>CF-01</t>
         </is>
       </c>
       <c r="B58" s="7" t="inlineStr">
@@ -4895,9 +4899,9 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="D58" s="8" t="inlineStr">
-        <is>
-          <t>보험료납입증명서</t>
+      <c r="D58" s="18" t="inlineStr">
+        <is>
+          <t>소득/세액공제 납입증명서</t>
         </is>
       </c>
       <c r="E58" s="9" t="inlineStr">
@@ -4922,12 +4926,12 @@
       </c>
       <c r="I58" s="13" t="inlineStr">
         <is>
-          <t>계약 목록, 납입기간별 납입액</t>
+          <t>대상 연도, 계약별 공제대상 납입액</t>
         </is>
       </c>
       <c r="J58" s="13" t="inlineStr">
         <is>
-          <t>계약, 기간, 용도, 수신방법</t>
+          <t>연도, 수신방법(출력·PDF·이메일·팩스)</t>
         </is>
       </c>
       <c r="K58" s="13" t="inlineStr">
@@ -4955,7 +4959,7 @@
     <row r="59">
       <c r="A59" s="5" t="inlineStr">
         <is>
-          <t>CF-03</t>
+          <t>CF-02</t>
         </is>
       </c>
       <c r="B59" s="7" t="inlineStr">
@@ -4970,7 +4974,7 @@
       </c>
       <c r="D59" s="8" t="inlineStr">
         <is>
-          <t>보험증권재발급</t>
+          <t>보험료납입증명서</t>
         </is>
       </c>
       <c r="E59" s="9" t="inlineStr">
@@ -4995,12 +4999,12 @@
       </c>
       <c r="I59" s="13" t="inlineStr">
         <is>
-          <t>계약 목록</t>
+          <t>계약 목록, 납입기간별 납입액</t>
         </is>
       </c>
       <c r="J59" s="13" t="inlineStr">
         <is>
-          <t>계약, 수신방법</t>
+          <t>계약, 기간, 용도, 수신방법</t>
         </is>
       </c>
       <c r="K59" s="13" t="inlineStr">
@@ -5010,7 +5014,7 @@
       </c>
       <c r="L59" s="9" t="inlineStr">
         <is>
-          <t>보전</t>
+          <t>수금</t>
         </is>
       </c>
       <c r="M59" s="10" t="inlineStr">
@@ -5020,7 +5024,7 @@
       </c>
       <c r="N59" s="16" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="O59" s="10" t="n"/>
@@ -5028,7 +5032,7 @@
     <row r="60">
       <c r="A60" s="5" t="inlineStr">
         <is>
-          <t>CF-04</t>
+          <t>CF-03</t>
         </is>
       </c>
       <c r="B60" s="7" t="inlineStr">
@@ -5043,7 +5047,7 @@
       </c>
       <c r="D60" s="8" t="inlineStr">
         <is>
-          <t>해지환급금증명서</t>
+          <t>보험증권재발급</t>
         </is>
       </c>
       <c r="E60" s="9" t="inlineStr">
@@ -5068,12 +5072,12 @@
       </c>
       <c r="I60" s="13" t="inlineStr">
         <is>
-          <t>계약 목록, 기준일 해지환급금</t>
+          <t>계약 목록</t>
         </is>
       </c>
       <c r="J60" s="13" t="inlineStr">
         <is>
-          <t>계약, 기준일, 수신방법</t>
+          <t>계약, 수신방법</t>
         </is>
       </c>
       <c r="K60" s="13" t="inlineStr">
@@ -5081,9 +5085,9 @@
           <t>즉시 발급</t>
         </is>
       </c>
-      <c r="L60" s="12" t="inlineStr">
-        <is>
-          <t>지급</t>
+      <c r="L60" s="9" t="inlineStr">
+        <is>
+          <t>보전</t>
         </is>
       </c>
       <c r="M60" s="10" t="inlineStr">
@@ -5093,7 +5097,7 @@
       </c>
       <c r="N60" s="16" t="inlineStr">
         <is>
-          <t>있음</t>
+          <t>없음</t>
         </is>
       </c>
       <c r="O60" s="10" t="n"/>
@@ -5101,7 +5105,7 @@
     <row r="61">
       <c r="A61" s="5" t="inlineStr">
         <is>
-          <t>CF-05</t>
+          <t>CF-04</t>
         </is>
       </c>
       <c r="B61" s="7" t="inlineStr">
@@ -5114,9 +5118,9 @@
           <t>보험</t>
         </is>
       </c>
-      <c r="D61" s="19" t="inlineStr">
-        <is>
-          <t>사고보험금지급명세</t>
+      <c r="D61" s="8" t="inlineStr">
+        <is>
+          <t>해지환급금증명서</t>
         </is>
       </c>
       <c r="E61" s="9" t="inlineStr">
@@ -5139,14 +5143,14 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I61" s="15" t="inlineStr">
-        <is>
-          <t>청구사항 목록, 지급설명서</t>
-        </is>
-      </c>
-      <c r="J61" s="15" t="inlineStr">
-        <is>
-          <t>청구, 지급일, 수신방법</t>
+      <c r="I61" s="13" t="inlineStr">
+        <is>
+          <t>계약 목록, 기준일 해지환급금</t>
+        </is>
+      </c>
+      <c r="J61" s="13" t="inlineStr">
+        <is>
+          <t>계약, 기준일, 수신방법</t>
         </is>
       </c>
       <c r="K61" s="13" t="inlineStr">
@@ -5156,7 +5160,7 @@
       </c>
       <c r="L61" s="12" t="inlineStr">
         <is>
-          <t>사고</t>
+          <t>지급</t>
         </is>
       </c>
       <c r="M61" s="10" t="inlineStr">
@@ -5166,7 +5170,7 @@
       </c>
       <c r="N61" s="16" t="inlineStr">
         <is>
-          <t>없음</t>
+          <t>있음</t>
         </is>
       </c>
       <c r="O61" s="10" t="n"/>
@@ -5174,7 +5178,7 @@
     <row r="62">
       <c r="A62" s="5" t="inlineStr">
         <is>
-          <t>CF-06</t>
+          <t>CF-05</t>
         </is>
       </c>
       <c r="B62" s="7" t="inlineStr">
@@ -5184,12 +5188,12 @@
       </c>
       <c r="C62" s="7" t="inlineStr">
         <is>
-          <t>대출</t>
-        </is>
-      </c>
-      <c r="D62" s="18" t="inlineStr">
-        <is>
-          <t>보험계약대출 증명서</t>
+          <t>보험</t>
+        </is>
+      </c>
+      <c r="D62" s="19" t="inlineStr">
+        <is>
+          <t>사고보험금지급명세</t>
         </is>
       </c>
       <c r="E62" s="9" t="inlineStr">
@@ -5204,7 +5208,7 @@
       </c>
       <c r="G62" s="11" t="inlineStr">
         <is>
-          <t>차주</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H62" s="12" t="inlineStr">
@@ -5212,14 +5216,14 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I62" s="13" t="inlineStr">
-        <is>
-          <t>보험계약대출 목록, 잔액·거래내역</t>
+      <c r="I62" s="15" t="inlineStr">
+        <is>
+          <t>청구사항 목록, 지급설명서</t>
         </is>
       </c>
       <c r="J62" s="15" t="inlineStr">
         <is>
-          <t>기준일·기간, 수신방법</t>
+          <t>청구, 지급일, 수신방법</t>
         </is>
       </c>
       <c r="K62" s="13" t="inlineStr">
@@ -5227,9 +5231,9 @@
           <t>즉시 발급</t>
         </is>
       </c>
-      <c r="L62" s="9" t="inlineStr">
-        <is>
-          <t>대출</t>
+      <c r="L62" s="12" t="inlineStr">
+        <is>
+          <t>사고</t>
         </is>
       </c>
       <c r="M62" s="10" t="inlineStr">
@@ -5239,30 +5243,30 @@
       </c>
       <c r="N62" s="16" t="inlineStr">
         <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O62" s="20" t="n"/>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O62" s="10" t="n"/>
     </row>
     <row r="63">
       <c r="A63" s="5" t="inlineStr">
         <is>
-          <t>CS-01</t>
-        </is>
-      </c>
-      <c r="B63" s="6" t="inlineStr">
-        <is>
-          <t>서류·안내</t>
-        </is>
-      </c>
-      <c r="C63" s="6" t="inlineStr">
-        <is>
-          <t>제지급/신청서류</t>
-        </is>
-      </c>
-      <c r="D63" s="19" t="inlineStr">
-        <is>
-          <t>사고보험금 청구서류</t>
+          <t>CF-06</t>
+        </is>
+      </c>
+      <c r="B63" s="7" t="inlineStr">
+        <is>
+          <t>증명서발급</t>
+        </is>
+      </c>
+      <c r="C63" s="7" t="inlineStr">
+        <is>
+          <t>대출</t>
+        </is>
+      </c>
+      <c r="D63" s="18" t="inlineStr">
+        <is>
+          <t>보험계약대출 증명서</t>
         </is>
       </c>
       <c r="E63" s="9" t="inlineStr">
@@ -5277,22 +5281,22 @@
       </c>
       <c r="G63" s="11" t="inlineStr">
         <is>
-          <t>청구인</t>
+          <t>차주</t>
         </is>
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>A0 비로그인</t>
-        </is>
-      </c>
-      <c r="I63" s="15" t="inlineStr">
-        <is>
-          <t>사고보험금 청구서류 목록</t>
-        </is>
-      </c>
-      <c r="J63" s="21" t="inlineStr">
-        <is>
-          <t>청구서류 종류(출럭 PDF)</t>
+          <t>A1 인증서</t>
+        </is>
+      </c>
+      <c r="I63" s="13" t="inlineStr">
+        <is>
+          <t>보험계약대출 목록, 잔액·거래내역</t>
+        </is>
+      </c>
+      <c r="J63" s="15" t="inlineStr">
+        <is>
+          <t>기준일·기간, 수신방법</t>
         </is>
       </c>
       <c r="K63" s="13" t="inlineStr">
@@ -5300,9 +5304,9 @@
           <t>즉시 발급</t>
         </is>
       </c>
-      <c r="L63" s="12" t="inlineStr">
-        <is>
-          <t>사고</t>
+      <c r="L63" s="9" t="inlineStr">
+        <is>
+          <t>대출</t>
         </is>
       </c>
       <c r="M63" s="10" t="inlineStr">
@@ -5312,83 +5316,156 @@
       </c>
       <c r="N63" s="16" t="inlineStr">
         <is>
-          <t>미확인</t>
-        </is>
-      </c>
-      <c r="O63" s="11" t="n"/>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O63" s="20" t="n"/>
     </row>
     <row r="64">
       <c r="A64" s="5" t="inlineStr">
         <is>
+          <t>CS-01</t>
+        </is>
+      </c>
+      <c r="B64" s="6" t="inlineStr">
+        <is>
+          <t>서류·안내</t>
+        </is>
+      </c>
+      <c r="C64" s="6" t="inlineStr">
+        <is>
+          <t>제지급/신청서류</t>
+        </is>
+      </c>
+      <c r="D64" s="19" t="inlineStr">
+        <is>
+          <t>사고보험금 청구서류</t>
+        </is>
+      </c>
+      <c r="E64" s="9" t="inlineStr">
+        <is>
+          <t>발급</t>
+        </is>
+      </c>
+      <c r="F64" s="10" t="inlineStr">
+        <is>
+          <t>T5 발급</t>
+        </is>
+      </c>
+      <c r="G64" s="11" t="inlineStr">
+        <is>
+          <t>청구인</t>
+        </is>
+      </c>
+      <c r="H64" s="12" t="inlineStr">
+        <is>
+          <t>A0 비로그인</t>
+        </is>
+      </c>
+      <c r="I64" s="15" t="inlineStr">
+        <is>
+          <t>사고보험금 청구서류 목록</t>
+        </is>
+      </c>
+      <c r="J64" s="21" t="inlineStr">
+        <is>
+          <t>청구서류 종류(출럭 PDF)</t>
+        </is>
+      </c>
+      <c r="K64" s="13" t="inlineStr">
+        <is>
+          <t>즉시 발급</t>
+        </is>
+      </c>
+      <c r="L64" s="12" t="inlineStr">
+        <is>
+          <t>사고</t>
+        </is>
+      </c>
+      <c r="M64" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N64" s="16" t="inlineStr">
+        <is>
+          <t>미확인</t>
+        </is>
+      </c>
+      <c r="O64" s="11" t="n"/>
+    </row>
+    <row r="65">
+      <c r="A65" s="5" t="inlineStr">
+        <is>
           <t>CS-02</t>
         </is>
       </c>
-      <c r="B64" s="6" t="inlineStr">
+      <c r="B65" s="6" t="inlineStr">
         <is>
           <t>서류·안내</t>
         </is>
       </c>
-      <c r="C64" s="6" t="inlineStr">
+      <c r="C65" s="6" t="inlineStr">
         <is>
           <t>제지급/신청서류</t>
         </is>
       </c>
-      <c r="D64" s="19" t="inlineStr">
+      <c r="D65" s="19" t="inlineStr">
         <is>
           <t>제지급 서류</t>
         </is>
       </c>
-      <c r="E64" s="9" t="inlineStr">
+      <c r="E65" s="9" t="inlineStr">
         <is>
           <t>발급</t>
         </is>
       </c>
-      <c r="F64" s="10" t="inlineStr">
+      <c r="F65" s="10" t="inlineStr">
         <is>
           <t>T5 발급</t>
         </is>
       </c>
-      <c r="G64" s="11" t="inlineStr">
+      <c r="G65" s="11" t="inlineStr">
         <is>
           <t>청구인</t>
         </is>
       </c>
-      <c r="H64" s="12" t="inlineStr">
+      <c r="H65" s="12" t="inlineStr">
         <is>
           <t>A0 비로그인</t>
         </is>
       </c>
-      <c r="I64" s="15" t="inlineStr">
+      <c r="I65" s="15" t="inlineStr">
         <is>
           <t>제지급 서류 목록</t>
         </is>
       </c>
-      <c r="J64" s="21" t="inlineStr">
+      <c r="J65" s="21" t="inlineStr">
         <is>
           <t>청구서류 종류(출럭 PDF)</t>
         </is>
       </c>
-      <c r="K64" s="13" t="inlineStr">
+      <c r="K65" s="13" t="inlineStr">
         <is>
           <t>즉시 발급</t>
         </is>
       </c>
-      <c r="L64" s="12" t="inlineStr">
+      <c r="L65" s="12" t="inlineStr">
         <is>
           <t>지급</t>
         </is>
       </c>
-      <c r="M64" s="10" t="inlineStr">
+      <c r="M65" s="10" t="inlineStr">
         <is>
           <t>-</t>
         </is>
       </c>
-      <c r="N64" s="16" t="inlineStr">
+      <c r="N65" s="16" t="inlineStr">
         <is>
           <t>미확인</t>
         </is>
       </c>
-      <c r="O64" s="11" t="n"/>
+      <c r="O65" s="11" t="n"/>
     </row>
   </sheetData>
   <autoFilter ref="A4:O64"/>
@@ -5818,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E59"/>
+  <dimension ref="A1:E61"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7371,6 +7448,60 @@
       <c r="E59" s="11" t="inlineStr">
         <is>
           <t>공통 하단</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B60" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C60" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D60" s="11" t="inlineStr">
+        <is>
+          <t>보험계약관리 3Depth 순서 변경: 계약관계자변경 → 보험기간/연금개시연도 변경 → 연금개시유형 선택/변경 → 연금전환 사전신청 → 변액보험 펀드변경/관리 → 감액완납 → 특약해지 → 보험계약 해지 → 대리청구인 지정/등록 → 금융정보보호 신청/해제 → 청약철회. 명칭 「대리청구인지정 등록」→「대리청구인 지정/등록」, 「청약 철회」→「청약철회」</t>
+        </is>
+      </c>
+      <c r="E60" s="11" t="inlineStr">
+        <is>
+          <t>CH-01~CH-10</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B61" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-13</t>
+        </is>
+      </c>
+      <c r="C61" s="11" t="inlineStr">
+        <is>
+          <t>추가</t>
+        </is>
+      </c>
+      <c r="D61" s="11" t="inlineStr">
+        <is>
+          <t>「연금전환 사전신청」 신규(T3): 종신보험 선택 → 전환 나이·연금 유형·지급 주기·계좌 입력, 전환 시점 예상 적립금·연금액(예시) → 사망보장 소멸·감소 동의 → 인증 → 접수 (업무 화면 52 → 53개)</t>
+        </is>
+      </c>
+      <c r="E61" s="11" t="inlineStr">
+        <is>
+          <t>CH-11(신규)</t>
         </is>
       </c>
     </row>

--- a/docs/메뉴정의서.xlsx
+++ b/docs/메뉴정의서.xlsx
@@ -3333,7 +3333,7 @@
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>PM-01</t>
+          <t>PY-10</t>
         </is>
       </c>
       <c r="B37" s="7" t="inlineStr">
@@ -3343,17 +3343,17 @@
       </c>
       <c r="C37" s="7" t="inlineStr">
         <is>
-          <t>보험료납입/자동이체</t>
+          <t>보험금청구/신청</t>
         </is>
       </c>
       <c r="D37" s="8" t="inlineStr">
         <is>
-          <t>보험료 납입 관리</t>
+          <t>연금전환 사전신청</t>
         </is>
       </c>
       <c r="E37" s="9" t="inlineStr">
         <is>
-          <t>입금</t>
+          <t>신청</t>
         </is>
       </c>
       <c r="F37" s="10" t="inlineStr">
@@ -3363,7 +3363,7 @@
       </c>
       <c r="G37" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>계약자(종신보험)</t>
         </is>
       </c>
       <c r="H37" s="12" t="inlineStr">
@@ -3373,40 +3373,44 @@
       </c>
       <c r="I37" s="13" t="inlineStr">
         <is>
-          <t>납입 대상 회차, 미납·연체 여부, 납입금액, 선납 할인</t>
-        </is>
-      </c>
-      <c r="J37" s="45" t="inlineStr">
-        <is>
-          <t>계약 선택, 납입 회차, 납입방법(계좌출금·가상계좌) / 납입 방법이 가상계좌면 발급 은행 선택(iM뱅크·농협), 내 계좌 출금이면 출금 계좌 선택</t>
-        </is>
-      </c>
-      <c r="K37" s="32" t="inlineStr">
-        <is>
-          <t>납입 완료 안내 / 가상계좌: 인증 후 「가상계좌 정보」(은행명·가상계좌번호(복사 버튼)·예금주명 「iM라이프」) + 이용안내(유효시간 내 입금, 입금 유효기간 신청일 오후 6시까지, 미입금 시 가상계좌 자동 폐기)</t>
+          <t>전환 가능 종신보험(적립금), 전환 시점 예상 적립금·연금액(예시)</t>
+        </is>
+      </c>
+      <c r="J37" s="13" t="inlineStr">
+        <is>
+          <t>대상 계약, 연금 전환 나이, 연금 유형, 지급 주기, 연금 받을 계좌</t>
+        </is>
+      </c>
+      <c r="K37" s="13" t="inlineStr">
+        <is>
+          <t>사전신청 접수·전환 예정일 30일 전 알림톡 안내</t>
         </is>
       </c>
       <c r="L37" s="9" t="inlineStr">
         <is>
-          <t>수금</t>
+          <t>보전</t>
         </is>
       </c>
       <c r="M37" s="10" t="inlineStr">
         <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N37" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O37" s="10" t="n"/>
+          <t>사망보장 소멸·감소 안내</t>
+        </is>
+      </c>
+      <c r="N37" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O37" s="10" t="inlineStr">
+        <is>
+          <t>v3.7 신규: 전환 예정일 전까지 변경·취소 가능 / 보험계약관리(CH-11) → 보험금청구/신청(PY-10) 이동</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="5" t="inlineStr">
         <is>
-          <t>PM-02</t>
+          <t>PM-01</t>
         </is>
       </c>
       <c r="B38" s="7" t="inlineStr">
@@ -3421,17 +3425,17 @@
       </c>
       <c r="D38" s="8" t="inlineStr">
         <is>
-          <t>보험료 자동이체 관리</t>
+          <t>보험료 납입 관리</t>
         </is>
       </c>
       <c r="E38" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>입금</t>
         </is>
       </c>
       <c r="F38" s="10" t="inlineStr">
         <is>
-          <t>T4 단일폼 변경</t>
+          <t>T3 단계형 신청</t>
         </is>
       </c>
       <c r="G38" s="11" t="inlineStr">
@@ -3441,22 +3445,22 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I38" s="13" t="inlineStr">
         <is>
-          <t>현재 이체 은행·계좌·이체일</t>
-        </is>
-      </c>
-      <c r="J38" s="13" t="inlineStr">
-        <is>
-          <t>은행, 계좌, 이체일</t>
-        </is>
-      </c>
-      <c r="K38" s="13" t="inlineStr">
-        <is>
-          <t>변경 완료 알림</t>
+          <t>납입 대상 회차, 미납·연체 여부, 납입금액, 선납 할인</t>
+        </is>
+      </c>
+      <c r="J38" s="45" t="inlineStr">
+        <is>
+          <t>계약 선택, 납입 회차, 납입방법(계좌출금·가상계좌) / 납입 방법이 가상계좌면 발급 은행 선택(iM뱅크·농협), 내 계좌 출금이면 출금 계좌 선택</t>
+        </is>
+      </c>
+      <c r="K38" s="32" t="inlineStr">
+        <is>
+          <t>납입 완료 안내 / 가상계좌: 인증 후 「가상계좌 정보」(은행명·가상계좌번호(복사 버튼)·예금주명 「iM라이프」) + 이용안내(유효시간 내 입금, 입금 유효기간 신청일 오후 6시까지, 미입금 시 가상계좌 자동 폐기)</t>
         </is>
       </c>
       <c r="L38" s="9" t="inlineStr">
@@ -3464,9 +3468,9 @@
           <t>수금</t>
         </is>
       </c>
-      <c r="M38" s="11" t="inlineStr">
-        <is>
-          <t>출금 동의(전자서명)</t>
+      <c r="M38" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
         </is>
       </c>
       <c r="N38" s="14" t="inlineStr">
@@ -3479,7 +3483,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>PM-03</t>
+          <t>PM-02</t>
         </is>
       </c>
       <c r="B39" s="7" t="inlineStr">
@@ -3494,7 +3498,7 @@
       </c>
       <c r="D39" s="8" t="inlineStr">
         <is>
-          <t>보험료 자동대출납입 신청/취소</t>
+          <t>보험료 자동이체 관리</t>
         </is>
       </c>
       <c r="E39" s="9" t="inlineStr">
@@ -3514,22 +3518,22 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I39" s="13" t="inlineStr">
         <is>
-          <t>신청 여부, 대출 가능금액, 적용이율</t>
+          <t>현재 이체 은행·계좌·이체일</t>
         </is>
       </c>
       <c r="J39" s="13" t="inlineStr">
         <is>
-          <t>신청·취소</t>
+          <t>은행, 계좌, 이체일</t>
         </is>
       </c>
       <c r="K39" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 안내</t>
+          <t>변경 완료 알림</t>
         </is>
       </c>
       <c r="L39" s="9" t="inlineStr">
@@ -3539,12 +3543,12 @@
       </c>
       <c r="M39" s="11" t="inlineStr">
         <is>
-          <t>대출 이자 발생 고지</t>
-        </is>
-      </c>
-      <c r="N39" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
+          <t>출금 동의(전자서명)</t>
+        </is>
+      </c>
+      <c r="N39" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
         </is>
       </c>
       <c r="O39" s="10" t="n"/>
@@ -3552,7 +3556,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>PM-04</t>
+          <t>PM-03</t>
         </is>
       </c>
       <c r="B40" s="7" t="inlineStr">
@@ -3567,22 +3571,22 @@
       </c>
       <c r="D40" s="8" t="inlineStr">
         <is>
-          <t>유니버설 자유납입 관리</t>
+          <t>보험료 자동대출납입 신청/취소</t>
         </is>
       </c>
       <c r="E40" s="9" t="inlineStr">
         <is>
-          <t>입금</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="F40" s="10" t="inlineStr">
         <is>
-          <t>T3 단계형 신청</t>
+          <t>T4 단일폼 변경</t>
         </is>
       </c>
       <c r="G40" s="11" t="inlineStr">
         <is>
-          <t>유니버설 계약자</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H40" s="12" t="inlineStr">
@@ -3592,17 +3596,17 @@
       </c>
       <c r="I40" s="13" t="inlineStr">
         <is>
-          <t>추가납입 한도·잔여 한도, 납입 일시중지 가능 여부</t>
+          <t>신청 여부, 대출 가능금액, 적용이율</t>
         </is>
       </c>
       <c r="J40" s="13" t="inlineStr">
         <is>
-          <t>추가납입 금액, 일시중지 신청</t>
+          <t>신청·취소</t>
         </is>
       </c>
       <c r="K40" s="13" t="inlineStr">
         <is>
-          <t>처리 완료 안내</t>
+          <t>변경 완료 안내</t>
         </is>
       </c>
       <c r="L40" s="9" t="inlineStr">
@@ -3612,12 +3616,12 @@
       </c>
       <c r="M40" s="11" t="inlineStr">
         <is>
-          <t>납입중지 시 월대체보험료 차감 고지</t>
-        </is>
-      </c>
-      <c r="N40" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
+          <t>대출 이자 발생 고지</t>
+        </is>
+      </c>
+      <c r="N40" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
         </is>
       </c>
       <c r="O40" s="10" t="n"/>
@@ -3625,7 +3629,7 @@
     <row r="41">
       <c r="A41" s="5" t="inlineStr">
         <is>
-          <t>CH-10</t>
+          <t>PM-04</t>
         </is>
       </c>
       <c r="B41" s="7" t="inlineStr">
@@ -3635,17 +3639,17 @@
       </c>
       <c r="C41" s="7" t="inlineStr">
         <is>
-          <t>보험계약관리</t>
-        </is>
-      </c>
-      <c r="D41" s="19" t="inlineStr">
-        <is>
-          <t>계약관계자변경</t>
+          <t>보험료납입/자동이체</t>
+        </is>
+      </c>
+      <c r="D41" s="8" t="inlineStr">
+        <is>
+          <t>유니버설 자유납입 관리</t>
         </is>
       </c>
       <c r="E41" s="9" t="inlineStr">
         <is>
-          <t>변경</t>
+          <t>입금</t>
         </is>
       </c>
       <c r="F41" s="10" t="inlineStr">
@@ -3655,37 +3659,37 @@
       </c>
       <c r="G41" s="11" t="inlineStr">
         <is>
-          <t>계약자(피보험자 동의 필요)</t>
+          <t>유니버설 계약자</t>
         </is>
       </c>
       <c r="H41" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서+추가인증</t>
+          <t>A1 인증서</t>
         </is>
       </c>
       <c r="I41" s="13" t="inlineStr">
         <is>
-          <t>현재 수익자(만기·사망·기타)</t>
+          <t>추가납입 한도·잔여 한도, 납입 일시중지 가능 여부</t>
         </is>
       </c>
       <c r="J41" s="13" t="inlineStr">
         <is>
-          <t>변경 수익자 정보, 피보험자 동의</t>
+          <t>추가납입 금액, 일시중지 신청</t>
         </is>
       </c>
       <c r="K41" s="13" t="inlineStr">
         <is>
-          <t>변경 완료 안내</t>
+          <t>처리 완료 안내</t>
         </is>
       </c>
       <c r="L41" s="9" t="inlineStr">
         <is>
-          <t>보전</t>
+          <t>수금</t>
         </is>
       </c>
       <c r="M41" s="11" t="inlineStr">
         <is>
-          <t>사망수익자 변경 시 피보험자 동의(상법)</t>
+          <t>납입중지 시 월대체보험료 차감 고지</t>
         </is>
       </c>
       <c r="N41" s="14" t="inlineStr">
@@ -3698,7 +3702,7 @@
     <row r="42">
       <c r="A42" s="5" t="inlineStr">
         <is>
-          <t>CH-05</t>
+          <t>CH-10</t>
         </is>
       </c>
       <c r="B42" s="7" t="inlineStr">
@@ -3711,9 +3715,9 @@
           <t>보험계약관리</t>
         </is>
       </c>
-      <c r="D42" s="8" t="inlineStr">
-        <is>
-          <t>보험기간/연금개시연도 변경</t>
+      <c r="D42" s="19" t="inlineStr">
+        <is>
+          <t>계약관계자변경</t>
         </is>
       </c>
       <c r="E42" s="9" t="inlineStr">
@@ -3728,22 +3732,22 @@
       </c>
       <c r="G42" s="11" t="inlineStr">
         <is>
-          <t>계약자</t>
+          <t>계약자(피보험자 동의 필요)</t>
         </is>
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>A1 인증서</t>
+          <t>A1 인증서+추가인증</t>
         </is>
       </c>
       <c r="I42" s="13" t="inlineStr">
         <is>
-          <t>연금 계약 카드(현재 연금개시 나이·일자, 납입 현황, 적립금), 변경 가능 범위(55~80세)</t>
+          <t>현재 수익자(만기·사망·기타)</t>
         </is>
       </c>
       <c r="J42" s="13" t="inlineStr">
         <is>
-          <t>대상 계약(카드 라디오 선택), 변경 후 연금개시 나이</t>
+          <t>변경 수익자 정보, 피보험자 동의</t>
         </is>
       </c>
       <c r="K42" s="13" t="inlineStr">
@@ -3756,26 +3760,22 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M42" s="10" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="N42" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O42" s="10" t="inlineStr">
-        <is>
-          <t>선택 → 입력 → 인증 → 완료 (확인 단계 생략)</t>
-        </is>
-      </c>
+      <c r="M42" s="11" t="inlineStr">
+        <is>
+          <t>사망수익자 변경 시 피보험자 동의(상법)</t>
+        </is>
+      </c>
+      <c r="N42" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O42" s="10" t="n"/>
     </row>
     <row r="43">
       <c r="A43" s="5" t="inlineStr">
         <is>
-          <t>CH-07</t>
+          <t>CH-05</t>
         </is>
       </c>
       <c r="B43" s="7" t="inlineStr">
@@ -3790,7 +3790,7 @@
       </c>
       <c r="D43" s="8" t="inlineStr">
         <is>
-          <t>연금개시유형 선택/변경</t>
+          <t>보험기간/연금개시연도 변경</t>
         </is>
       </c>
       <c r="E43" s="9" t="inlineStr">
@@ -3805,7 +3805,7 @@
       </c>
       <c r="G43" s="11" t="inlineStr">
         <is>
-          <t>연금 계약자</t>
+          <t>계약자</t>
         </is>
       </c>
       <c r="H43" s="12" t="inlineStr">
@@ -3813,14 +3813,14 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I43" s="32" t="inlineStr">
-        <is>
-          <t>연금 계약(선택 단계), 선택 요약·월 환산 예상액·회당 예상 연금액(지급주기 반영, 예시)</t>
-        </is>
-      </c>
-      <c r="J43" s="32" t="inlineStr">
-        <is>
-          <t>연금유형, 개인형/부부형, 연금비율, 체증형태, 체증기간, 체증율, 확정기간, 보증기간, 지급주기, 조기집중형보장배수 (10개 선택조건)</t>
+      <c r="I43" s="13" t="inlineStr">
+        <is>
+          <t>연금 계약 카드(현재 연금개시 나이·일자, 납입 현황, 적립금), 변경 가능 범위(55~80세)</t>
+        </is>
+      </c>
+      <c r="J43" s="13" t="inlineStr">
+        <is>
+          <t>대상 계약(카드 라디오 선택), 변경 후 연금개시 나이</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
@@ -3833,26 +3833,26 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M43" s="33" t="inlineStr">
-        <is>
-          <t>개시 후 변경 제한 고지 / 예상 연금액은 예시(확정 아님)</t>
-        </is>
-      </c>
-      <c r="N43" s="14" t="inlineStr">
-        <is>
-          <t>있음</t>
-        </is>
-      </c>
-      <c r="O43" s="34" t="inlineStr">
-        <is>
-          <t>v3.3: 연금유형별 고정값 규칙 적용(상세: 「선택조건_CH-07」 시트) · 고정 항목은 고정값만 표시·선택 불가 · 입력 영역 PC 2열/모바일 2열(긴 항목 1열) 촘촘한 버튼형 배치</t>
+      <c r="M43" s="10" t="inlineStr">
+        <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="N43" s="16" t="inlineStr">
+        <is>
+          <t>없음</t>
+        </is>
+      </c>
+      <c r="O43" s="10" t="inlineStr">
+        <is>
+          <t>선택 → 입력 → 인증 → 완료 (확인 단계 생략)</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="5" t="inlineStr">
         <is>
-          <t>CH-11</t>
+          <t>CH-07</t>
         </is>
       </c>
       <c r="B44" s="7" t="inlineStr">
@@ -3867,12 +3867,12 @@
       </c>
       <c r="D44" s="8" t="inlineStr">
         <is>
-          <t>연금전환 사전신청</t>
+          <t>연금개시유형 선택/변경</t>
         </is>
       </c>
       <c r="E44" s="9" t="inlineStr">
         <is>
-          <t>신청</t>
+          <t>변경</t>
         </is>
       </c>
       <c r="F44" s="10" t="inlineStr">
@@ -3882,7 +3882,7 @@
       </c>
       <c r="G44" s="11" t="inlineStr">
         <is>
-          <t>계약자(종신보험)</t>
+          <t>연금 계약자</t>
         </is>
       </c>
       <c r="H44" s="12" t="inlineStr">
@@ -3890,19 +3890,19 @@
           <t>A1 인증서</t>
         </is>
       </c>
-      <c r="I44" s="13" t="inlineStr">
-        <is>
-          <t>전환 가능 종신보험(적립금), 전환 시점 예상 적립금·연금액(예시)</t>
-        </is>
-      </c>
-      <c r="J44" s="13" t="inlineStr">
-        <is>
-          <t>대상 계약, 연금 전환 나이, 연금 유형, 지급 주기, 연금 받을 계좌</t>
+      <c r="I44" s="32" t="inlineStr">
+        <is>
+          <t>연금 계약(선택 단계), 선택 요약·월 환산 예상액·회당 예상 연금액(지급주기 반영, 예시)</t>
+        </is>
+      </c>
+      <c r="J44" s="32" t="inlineStr">
+        <is>
+          <t>연금유형, 개인형/부부형, 연금비율, 체증형태, 체증기간, 체증율, 확정기간, 보증기간, 지급주기, 조기집중형보장배수 (10개 선택조건)</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>사전신청 접수·전환 예정일 30일 전 알림톡 안내</t>
+          <t>변경 완료 안내</t>
         </is>
       </c>
       <c r="L44" s="9" t="inlineStr">
@@ -3910,19 +3910,19 @@
           <t>보전</t>
         </is>
       </c>
-      <c r="M44" s="10" t="inlineStr">
-        <is>
-          <t>사망보장 소멸·감소 안내</t>
-        </is>
-      </c>
-      <c r="N44" s="16" t="inlineStr">
-        <is>
-          <t>없음</t>
-        </is>
-      </c>
-      <c r="O44" s="10" t="inlineStr">
-        <is>
-          <t>v3.7 신규: 전환 예정일 전까지 변경·취소 가능</t>
+      <c r="M44" s="33" t="inlineStr">
+        <is>
+          <t>개시 후 변경 제한 고지 / 예상 연금액은 예시(확정 아님)</t>
+        </is>
+      </c>
+      <c r="N44" s="14" t="inlineStr">
+        <is>
+          <t>있음</t>
+        </is>
+      </c>
+      <c r="O44" s="34" t="inlineStr">
+        <is>
+          <t>v3.3: 연금유형별 고정값 규칙 적용(상세: 「선택조건_CH-07」 시트) · 고정 항목은 고정값만 표시·선택 불가 · 입력 영역 PC 2열/모바일 2열(긴 항목 1열) 촘촘한 버튼형 배치</t>
         </is>
       </c>
     </row>
@@ -5895,7 +5895,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E61"/>
+  <dimension ref="A1:E62"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" min="1" max="1"/>
@@ -7502,6 +7502,33 @@
       <c r="E61" s="11" t="inlineStr">
         <is>
           <t>CH-11(신규)</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" s="11" t="inlineStr">
+        <is>
+          <t>v3.7</t>
+        </is>
+      </c>
+      <c r="B62" s="11" t="inlineStr">
+        <is>
+          <t>2026-10-15</t>
+        </is>
+      </c>
+      <c r="C62" s="11" t="inlineStr">
+        <is>
+          <t>변경</t>
+        </is>
+      </c>
+      <c r="D62" s="11" t="inlineStr">
+        <is>
+          <t>「연금전환 사전신청」을 보험계약관리에서 보험금청구/신청 「연금 지급 신청」 뒤로 이동, 메뉴ID CH-11 → PY-10</t>
+        </is>
+      </c>
+      <c r="E62" s="11" t="inlineStr">
+        <is>
+          <t>PY-10(구 CH-11)</t>
         </is>
       </c>
     </row>
